--- a/public/templates/CITYBUS-BAO-CAO-TOC-DO-4H-BP-QLCL-DV.xlsx
+++ b/public/templates/CITYBUS-BAO-CAO-TOC-DO-4H-BP-QLCL-DV.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11110"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12418F45-39BA-DE40-A0D5-5F8160584241}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9805F609-4CC0-6247-8A43-3B63E6F30125}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="740" yWindow="740" windowWidth="28060" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,10 +88,6 @@
     <t>3. Khó khăn/ đề xuất</t>
   </si>
   <si>
-    <t>BÁO CÁO CÔNG VIỆC BỘ PHẬN QUẢN LÝ CLDV CITYBUS
-(Từ ngày ... đến ngày ...)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Họ &amp; tên: </t>
   </si>
   <si>
@@ -101,13 +97,30 @@
   <si>
     <t xml:space="preserve">b) Ý kiến đề xuất:
 </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BÁO CÁO CÔNG VIỆC BỘ PHẬN QUẢN LÝ CLDV CITYBUS
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(Từ ngày ... đến ngày ...)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +188,21 @@
       <b/>
       <i/>
       <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -309,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -347,34 +375,37 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -660,99 +691,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+    </row>
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+    </row>
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="1:11" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-    </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-    </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17" t="s">
+      <c r="G6" s="21"/>
+      <c r="H6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="17"/>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
@@ -780,12 +811,12 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
       <c r="E9" s="9"/>
       <c r="F9" s="8"/>
       <c r="G9" s="10">
@@ -804,53 +835,53 @@
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17" t="s">
+      <c r="G11" s="16"/>
+      <c r="H11" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="17"/>
+      <c r="I11" s="16"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="17"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="21"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="17"/>
       <c r="F12" s="11" t="s">
         <v>9</v>
       </c>
@@ -880,12 +911,12 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
       <c r="E14" s="9"/>
       <c r="F14" s="8"/>
       <c r="G14" s="10">
@@ -902,101 +933,112 @@
       </c>
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
     </row>
     <row r="16" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
     </row>
     <row r="17" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
     </row>
     <row r="18" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="20"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="20" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="20"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
     </row>
     <row r="21" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
     </row>
     <row r="22" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="E16:I22"/>
@@ -1010,17 +1052,6 @@
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
